--- a/Spa Manager/Grading/2 stage/6-examples/Spa-Manager_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_GPT5.5AutoGrading.xlsx
+++ b/Spa Manager/Grading/2 stage/6-examples/Spa-Manager_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_GPT5.5AutoGrading.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="24220" yWindow="-21000" windowWidth="30240" windowHeight="17300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spa Manager" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gemini Generation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Spa Manager" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="GPT-5.5 Grading" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Metrics" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -5742,7 +5742,7 @@
       </c>
       <c r="C1" s="12" t="inlineStr">
         <is>
-          <t>GPT-5</t>
+          <t>Grading</t>
         </is>
       </c>
       <c r="D1" s="13" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="D2" s="15" t="inlineStr">
         <is>
-          <t>Present as the top-level composite state containing both SaunaController and JacuzziController regions.</t>
+          <t>Top level composite SpaManager is present.</t>
         </is>
       </c>
     </row>
@@ -5787,7 +5787,7 @@
       </c>
       <c r="D3" s="15" t="inlineStr">
         <is>
-          <t>Present as JacuzziController region within SpaManager.</t>
+          <t>Jacuzzi behavior is separated in its own region.</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="D4" s="15" t="inlineStr">
         <is>
-          <t>Initial state correctly transitions to JacuzziOff.</t>
+          <t>Jacuzzi region initializes to JacuzziOff.</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>JacuzziOn composite state is present with nested regions.</t>
+          <t>JacuzziOn composite state is present.</t>
         </is>
       </c>
     </row>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>Transitions centralTurnJacuzziOn and panelTurnJacuzziOn correctly turn on the Jacuzzi.</t>
+          <t>JacuzziOff transitions to JacuzziOn on turnOnJacuzzi.</t>
         </is>
       </c>
     </row>
@@ -5887,7 +5887,7 @@
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>Transitions centralTurnJacuzziOff and panelTurnJacuzziOff correctly turn off the Jacuzzi.</t>
+          <t>JacuzziOn transitions to JacuzziOff on turnOffJacuzzi.</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>Initial state in PressureControl region correctly transitions to Level1.</t>
+          <t>Pressure region initializes to Level1 when active.</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>Level1 state is present in PressureControl region.</t>
+          <t>Low pressure Level1 state is present.</t>
         </is>
       </c>
     </row>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>Transitions centralIncreasePressure and panelIncreasePressure correctly move from Level1 to Level2.</t>
+          <t>Increase transition from Level1 to Level2 is present.</t>
         </is>
       </c>
     </row>
@@ -5967,7 +5967,7 @@
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>Level2 state is present in PressureControl region.</t>
+          <t>Medium pressure Level2 state is present.</t>
         </is>
       </c>
     </row>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="D13" s="15" t="inlineStr">
         <is>
-          <t>Transitions centralIncreasePressure and panelIncreasePressure correctly move from Level2 to Level3.</t>
+          <t>Increase transition from Level2 to Level3 is present.</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>Transitions centralDecreasePressure and panelDecreasePressure correctly move from Level2 to Level1.</t>
+          <t>Decrease transition from Level2 to Level1 is present.</t>
         </is>
       </c>
     </row>
@@ -6027,7 +6027,7 @@
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>Level3 state is present in PressureControl region.</t>
+          <t>High pressure Level3 state is present.</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>Transitions centralDecreasePressure and panelDecreasePressure correctly move from Level3 to Level2.</t>
+          <t>Decrease transition from Level3 to Level2 is present.</t>
         </is>
       </c>
     </row>
@@ -6063,11 +6063,11 @@
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>No history state is present in the student submission.</t>
+          <t>H state is included and used as the return target after pause.</t>
         </is>
       </c>
     </row>
@@ -6083,11 +6083,11 @@
         </is>
       </c>
       <c r="C18" s="14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>Pattern selection is modeled as internal transitions within PatternConfigured state rather than transitions to history state.</t>
+          <t>Pattern selection is modeled with a guarded selectPattern transition while preserving active behavior.</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>JetsPaused state is present in JetOperation region.</t>
+          <t>JacuzziPaused state is present.</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>Transitions centralPauseJets and panelPauseJets correctly move from JetsRunning to JetsPaused.</t>
+          <t>Pause transition from active Jacuzzi operation to JacuzziPaused is present.</t>
         </is>
       </c>
     </row>
@@ -6139,15 +6139,15 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>after 2min  (Paused ⇒ History State)</t>
+          <t>after 2min (Paused ⇒ History State)</t>
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>After 2min transition returns to JetsRunning but not via history state.</t>
+          <t>JacuzziPaused returns to H after 2 minutes.</t>
         </is>
       </c>
     </row>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>Present as SaunaController region within SpaManager.</t>
+          <t>Sauna behavior is separated in its own region.</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>Initial state correctly transitions to SaunaOff.</t>
+          <t>Sauna region initializes to SaunaOff.</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>SaunaOn composite state is present with nested regions.</t>
+          <t>SaunaOn composite state is present.</t>
         </is>
       </c>
     </row>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>Transition centralTurnSaunaOn correctly turns on the sauna.</t>
+          <t>SaunaOff transitions to SaunaOn on turnOnSauna.</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>Transition centralTurnSaunaOff correctly turns off the sauna.</t>
+          <t>SaunaOn transitions to SaunaOff on turnOffSauna.</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="D28" s="15" t="inlineStr">
         <is>
-          <t>Present as TemperatureControl region within SaunaOn.</t>
+          <t>Heating behavior is modeled in a separate region.</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>Initial state correctly transitions to TemperatureHeating.</t>
+          <t>Heating region initializes to HeatingOn.</t>
         </is>
       </c>
     </row>
@@ -6327,7 +6327,7 @@
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>TemperatureHeating state is present.</t>
+          <t>HeatingOn represents the stove heating state.</t>
         </is>
       </c>
     </row>
@@ -6347,7 +6347,7 @@
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>Transition from TemperatureHeating to TemperatureIdle is present.</t>
+          <t>HeatingOn transitions to HeatingOff when hot enough.</t>
         </is>
       </c>
     </row>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>Guard temperatureAtOrAbove90C correctly represents the 90 degree threshold.</t>
+          <t>The heating off transition uses temp &gt;= 90.</t>
         </is>
       </c>
     </row>
@@ -6387,7 +6387,7 @@
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>TemperatureIdle state is present.</t>
+          <t>HeatingOff represents the nonheating idle state.</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>Transition from TemperatureIdle to TemperatureHeating is present.</t>
+          <t>HeatingOff transitions back to HeatingOn when temperature drops.</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="D35" s="15" t="inlineStr">
         <is>
-          <t>Guard temperatureBelow85C correctly represents the 85 degree threshold.</t>
+          <t>The reheat transition uses temp &lt; 85.</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>Present as HumidityControl region within SaunaOn.</t>
+          <t>Fan behavior is modeled in a separate region.</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6467,7 @@
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>Initial state correctly transitions to HumiditySafe.</t>
+          <t>Fan region initializes to FanOff.</t>
         </is>
       </c>
     </row>
@@ -6487,7 +6487,7 @@
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>HumiditySafe state represents the fan off condition.</t>
+          <t>FanOff state is present.</t>
         </is>
       </c>
       <c r="E38" s="5" t="n"/>
@@ -6523,11 +6523,11 @@
         </is>
       </c>
       <c r="C39" s="14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
-          <t>Fan activation logic is present but modeled with intermediate HumidityAboveLimitTiming state and 3min timer before activation.</t>
+          <t>Fan activation after sustained high humidity is captured through FanMonitoring then after 3min to FanOn.</t>
         </is>
       </c>
       <c r="E39" s="5" t="n"/>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>Guard after3min with humidityPercent &gt; 40 correctly represents the humidity and time conditions.</t>
+          <t>High humidity condition and 3 minute duration are represented by guard plus timed transition.</t>
         </is>
       </c>
       <c r="E40" s="5" t="n"/>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="D41" s="15" t="inlineStr">
         <is>
-          <t>Present as WaterDispersal region within SaunaOn.</t>
+          <t>Water dispersion behavior is modeled in a separate region.</t>
         </is>
       </c>
       <c r="E41" s="5" t="n"/>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>Initial state correctly transitions to WaterReady.</t>
+          <t>Water region initializes to WaterReady which represents availability.</t>
         </is>
       </c>
       <c r="E42" s="5" t="n"/>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>WaterReady state is present.</t>
+          <t>WaterReady represents the idle ready state for dispensing.</t>
         </is>
       </c>
       <c r="E43" s="5" t="n"/>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>Self-transition on WaterReady with centralDisperseWaterRequest is present.</t>
+          <t>Dispensing is modeled as Ready to Cooldown then back after 15 minutes which is behaviorally equivalent.</t>
         </is>
       </c>
       <c r="E44" s="5" t="n"/>
@@ -6767,7 +6767,7 @@
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>Guard humidityPercent &lt; 40 &amp;&amp; fanInactive correctly represents the conditions; 15min cooldown is enforced via WaterCooldown state.</t>
+          <t>Humidity and fan guards are explicit and the cooldown state enforces the 15 minute limit.</t>
         </is>
       </c>
       <c r="E45" s="5" t="n"/>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="D46" s="18" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect states are present.</t>
+          <t>Extra states such as monitoring cooldown active and pattern selection are reasonable refinements.</t>
         </is>
       </c>
       <c r="E46" s="5" t="n"/>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="D47" s="18" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect transitions are present.</t>
+          <t>No fundamentally incorrect extra transitions are present.</t>
         </is>
       </c>
     </row>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect guards are present.</t>
+          <t>Extra guards such as valid pattern range and humidity reset are consistent with the description.</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>Actions are reasonable modeling choices for entry/exit/do behaviors.</t>
+          <t>Actions such as heat runFan setPattern and disperseWater are appropriate.</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>Additional composite states are reasonable modeling choices.</t>
+          <t>Additional composite structure for active Jacuzzi behavior is reasonable.</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6927,7 @@
       </c>
       <c r="D51" s="15" t="inlineStr">
         <is>
-          <t>No fundamentally incorrect regions are present.</t>
+          <t>Additional pressure and pattern regions are appropriate for independent Jacuzzi features.</t>
         </is>
       </c>
     </row>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>No history states are present in the student submission.</t>
+          <t>No incorrect extra history states are present.</t>
         </is>
       </c>
     </row>
@@ -11725,7 +11725,7 @@
     <row r="1" ht="15.75" customHeight="1" s="72">
       <c r="A1" s="73" t="inlineStr">
         <is>
-          <t>Generated by GPT-5</t>
+          <t>Generated by Gemini 3.1 Pro</t>
         </is>
       </c>
       <c r="J1" s="24" t="inlineStr">
@@ -11792,15 +11792,15 @@
         <v/>
       </c>
       <c r="C3" s="29">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$45, $A3, 'GPT-5 Generation'!$C$2:$C$45)</f>
+        <f>SUMIF('GPT-5.5 Grading'!$A$2:$A$45, $A3, 'GPT-5.5 Grading'!$C$2:$C$45)</f>
         <v/>
       </c>
       <c r="D3" s="29">
-        <f>SUMIF('GPT-5 Generation'!A$46:A$52, A3, 'GPT-5 Generation'!$C$46:$C$52)</f>
+        <f>SUMIF('GPT-5.5 Grading'!A$46:A$52, A3, 'GPT-5.5 Grading'!$C$46:$C$52)</f>
         <v/>
       </c>
       <c r="E3" s="29">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$45, $A3, 'GPT-5 Generation'!$C$2:$C$45,0)</f>
+        <f>COUNTIFS('GPT-5.5 Grading'!$A$2:$A$45, $A3, 'GPT-5.5 Grading'!$C$2:$C$45,0)</f>
         <v/>
       </c>
       <c r="F3" s="29">
@@ -11828,15 +11828,15 @@
         <v/>
       </c>
       <c r="C4" s="29">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$45, $A4, 'GPT-5 Generation'!$C$2:$C$45)</f>
+        <f>SUMIF('GPT-5.5 Grading'!$A$2:$A$45, $A4, 'GPT-5.5 Grading'!$C$2:$C$45)</f>
         <v/>
       </c>
       <c r="D4" s="29">
-        <f>SUMIF('GPT-5 Generation'!A$46:A$52, A4, 'GPT-5 Generation'!$C$46:$C$52)</f>
+        <f>SUMIF('GPT-5.5 Grading'!A$46:A$52, A4, 'GPT-5.5 Grading'!$C$46:$C$52)</f>
         <v/>
       </c>
       <c r="E4" s="29">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$45, $A4, 'GPT-5 Generation'!$C$2:$C$45,0)</f>
+        <f>COUNTIFS('GPT-5.5 Grading'!$A$2:$A$45, $A4, 'GPT-5.5 Grading'!$C$2:$C$45,0)</f>
         <v/>
       </c>
       <c r="F4" s="29">
@@ -11868,15 +11868,15 @@
         <v/>
       </c>
       <c r="C5" s="29">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$45, $A5, 'GPT-5 Generation'!$C$2:$C$45)</f>
+        <f>SUMIF('GPT-5.5 Grading'!$A$2:$A$45, $A5, 'GPT-5.5 Grading'!$C$2:$C$45)</f>
         <v/>
       </c>
       <c r="D5" s="29">
-        <f>SUMIF('GPT-5 Generation'!A$46:A$52, A5, 'GPT-5 Generation'!$C$46:$C$52)</f>
+        <f>SUMIF('GPT-5.5 Grading'!A$46:A$52, A5, 'GPT-5.5 Grading'!$C$46:$C$52)</f>
         <v/>
       </c>
       <c r="E5" s="29">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$45, $A5, 'GPT-5 Generation'!$C$2:$C$45,0)</f>
+        <f>COUNTIFS('GPT-5.5 Grading'!$A$2:$A$45, $A5, 'GPT-5.5 Grading'!$C$2:$C$45,0)</f>
         <v/>
       </c>
       <c r="F5" s="29">
@@ -11893,7 +11893,7 @@
       </c>
       <c r="J5" s="26" t="inlineStr">
         <is>
-          <t>GPT-5</t>
+          <t>GPT-5.5</t>
         </is>
       </c>
     </row>
@@ -11908,15 +11908,15 @@
         <v/>
       </c>
       <c r="C6" s="29">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$45, $A6, 'GPT-5 Generation'!$C$2:$C$45)</f>
+        <f>SUMIF('GPT-5.5 Grading'!$A$2:$A$45, $A6, 'GPT-5.5 Grading'!$C$2:$C$45)</f>
         <v/>
       </c>
       <c r="D6" s="29">
-        <f>SUMIF('GPT-5 Generation'!A$46:A$52, A6, 'GPT-5 Generation'!$C$46:$C$52)</f>
+        <f>SUMIF('GPT-5.5 Grading'!A$46:A$52, A6, 'GPT-5.5 Grading'!$C$46:$C$52)</f>
         <v/>
       </c>
       <c r="E6" s="29">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$45, $A6, 'GPT-5 Generation'!$C$2:$C$45,0)</f>
+        <f>COUNTIFS('GPT-5.5 Grading'!$A$2:$A$45, $A6, 'GPT-5.5 Grading'!$C$2:$C$45,0)</f>
         <v/>
       </c>
       <c r="F6" s="29">
@@ -11943,15 +11943,15 @@
         <v/>
       </c>
       <c r="C7" s="29">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$45, $A7, 'GPT-5 Generation'!$C$2:$C$45)</f>
+        <f>SUMIF('GPT-5.5 Grading'!$A$2:$A$45, $A7, 'GPT-5.5 Grading'!$C$2:$C$45)</f>
         <v/>
       </c>
       <c r="D7" s="29">
-        <f>SUMIF('GPT-5 Generation'!A$46:A$52, A7, 'GPT-5 Generation'!$C$46:$C$52)</f>
+        <f>SUMIF('GPT-5.5 Grading'!A$46:A$52, A7, 'GPT-5.5 Grading'!$C$46:$C$52)</f>
         <v/>
       </c>
       <c r="E7" s="29">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$45, $A7, 'GPT-5 Generation'!$C$2:$C$45,0)</f>
+        <f>COUNTIFS('GPT-5.5 Grading'!$A$2:$A$45, $A7, 'GPT-5.5 Grading'!$C$2:$C$45,0)</f>
         <v/>
       </c>
       <c r="F7" s="29">
@@ -11983,15 +11983,15 @@
         <v/>
       </c>
       <c r="C8" s="29">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$45, $A8, 'GPT-5 Generation'!$C$2:$C$45)</f>
+        <f>SUMIF('GPT-5.5 Grading'!$A$2:$A$45, $A8, 'GPT-5.5 Grading'!$C$2:$C$45)</f>
         <v/>
       </c>
       <c r="D8" s="29">
-        <f>SUMIF('GPT-5 Generation'!A$46:A$52, A8, 'GPT-5 Generation'!$C$46:$C$52)</f>
+        <f>SUMIF('GPT-5.5 Grading'!A$46:A$52, A8, 'GPT-5.5 Grading'!$C$46:$C$52)</f>
         <v/>
       </c>
       <c r="E8" s="29">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$45, $A8, 'GPT-5 Generation'!$C$2:$C$45,0)</f>
+        <f>COUNTIFS('GPT-5.5 Grading'!$A$2:$A$45, $A8, 'GPT-5.5 Grading'!$C$2:$C$45,0)</f>
         <v/>
       </c>
       <c r="F8" s="29">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="J8" s="70" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Gemini 3.1 Pro</t>
         </is>
       </c>
     </row>
@@ -12023,15 +12023,15 @@
         <v/>
       </c>
       <c r="C9" s="29">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$45, $A9, 'GPT-5 Generation'!$C$2:$C$45)</f>
+        <f>SUMIF('GPT-5.5 Grading'!$A$2:$A$45, $A9, 'GPT-5.5 Grading'!$C$2:$C$45)</f>
         <v/>
       </c>
       <c r="D9" s="29">
-        <f>SUMIF('GPT-5 Generation'!A$46:A$52, A9, 'GPT-5 Generation'!$C$46:$C$52)</f>
+        <f>SUMIF('GPT-5.5 Grading'!A$46:A$52, A9, 'GPT-5.5 Grading'!$C$46:$C$52)</f>
         <v/>
       </c>
       <c r="E9" s="29">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$45, $A9, 'GPT-5 Generation'!$C$2:$C$45,0)</f>
+        <f>COUNTIFS('GPT-5.5 Grading'!$A$2:$A$45, $A9, 'GPT-5.5 Grading'!$C$2:$C$45,0)</f>
         <v/>
       </c>
       <c r="F9" s="29">
